--- a/DOC/DataMapping.xlsx
+++ b/DOC/DataMapping.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -78,14 +78,8 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00375623"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -137,11 +131,6 @@
         <fgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -169,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -207,18 +196,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -828,11 +805,12 @@
     <row r="19" ht="34" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>1) 現行寫入邏輯為「INSERT-or-SKIP」：先查業務鍵是否存在，存在則跳過 (SKIP)，不存在才 INSERT。各資料表的 UPDATE 邏輯已寫在程式碼中但以註解停用，104 端資料異動後暫不會覆蓋 BPM/ERP 既有紀錄。
+          <t>1) 寫入邏輯為 UPSERT：先查業務鍵是否存在，不存在則 INSERT。2026-07-16 依客戶回覆 DataMappingUserConfirm20260716.xlsx，已針對客戶確認需要異動的欄位啟用 UPDATE 邏輯 (詳見 7/8/9 更新 Mapping 分頁)；未經客戶確認需要更新的欄位則維持原值不動，仍不會被覆蓋。
 2) BPM 所有 Table 的 OID 由 Guid.NewGuid().ToString("N") 產生 (32 碼小寫十六進位)，並確保系統中不重複。
 3) 部門資料寫入前會先做拓撲排序，確保父部門一定比子部門先寫入 BPM，以便子部門查到父部門的 OID。
 4) appsettings.json 的 HRApi.BaseDate 已於 2026-07-14 移除固定值設定，改為每次執行自動使用系統當天日期，避免因基準日過舊導致 104 API 查無資料 (曾造成部門層級同步誤判為權限錯誤)。
-5) 員工資料 104 端支援 5 層部門 (DEPT1_CODE ~ DEPT5_CODE)，目前程式僅使用第一層 DEPT1_CODE 作為員工所屬部門。</t>
+5) 員工資料 104 端支援 5 層部門 (DEPT1_CODE ~ DEPT5_CODE)，目前程式僅使用第一層 DEPT1_CODE 作為員工所屬部門。
+6) 2026-07-16 新增：ERP gen_file.TA_GEN07 (直屬主管工號) 由查詢 BPM OrganizationUnit.managerOID 取得；GEN04 (職稱) 曾評估改由 BPM Functions/FunctionDefinition 取得，2026-07-18 客戶回覆暫不實作，同步程式不觸碰 Functions 表；TA_GEN08 (銀行帳號) 因 104 員工 API 目前無此欄位，暫緩實作。</t>
         </is>
       </c>
     </row>
@@ -855,15 +833,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -876,14 +855,14 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>現行程式僅在員工已存在時「跳過(SKIP)」，並不會更新既有資料。以下請客戶確認：資料異動時應以哪個欄位判斷唯一值、需要更新哪些欄位。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
+          <t>2026-07-16 依客戶回覆 DataMappingUserConfirm20260716.xlsx 定案，程式已同步更新 UPDATE 邏輯。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>填寫說明：黃色儲存格為需要客戶確認/填寫的欄位。第一列(綠色斜體)為範例，僅供參考格式，非實際資料，正式填寫時請覆蓋或刪除。「是否需要更新」請填「是」或「否」；填「是」的欄位請在「更新規則/資料來源說明」註明依 104 哪個欄位、什麼條件更新。</t>
+          <t>2026-07-16 更新：客戶已於 DataMappingUserConfirm20260716.xlsx 回覆各欄位是否需要更新，本頁已依回覆內容定案。「實作狀態」欄位說明：綠色「已實作」代表程式已於 2026-07-16 加入對應 UPDATE 邏輯；橘色「暫緩」代表客戶雖回覆需要更新，但目前完全沒有資料來源可供寫入，貿然實作可能誤蓋既有資料，故暫緩，待補充資料來源後再開發；灰色「不需異動」代表客戶回覆或既有邏輯判斷不需要更新此欄位。</t>
         </is>
       </c>
     </row>
@@ -895,7 +874,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>id = 104 EMP_NO　（現行新增時查重複用此鍵，如需異動可在此欄修改）</t>
+          <t>id = 104 EMP_NO　（現行查重複/UPDATE 比對鍵，客戶未提出異動）</t>
         </is>
       </c>
     </row>
@@ -912,13 +891,13 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>104 來源欄位 / 現行新增邏輯</t>
+          <t>104 來源欄位 / 現行邏輯</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
           <t>資料異動時
-是否需要更新 (是/否)</t>
+是否需要更新</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -928,41 +907,48 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
+          <t>實作狀態
+(2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>leaveDate</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>datetime NULL</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>QUIT_DATE</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>104 QUIT_DATE 異動時（離職），覆蓋更新此欄位</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>範例列，正式填寫時請覆蓋</t>
-        </is>
-      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -980,11 +966,24 @@
           <t>EMP_NAME</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="17" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>改名時是否需要更新</t>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆確認需要更新</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>改名時同步更新</t>
         </is>
       </c>
     </row>
@@ -1004,9 +1003,22 @@
           <t>OFFICE_EMAIL</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="17" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆確認需要更新</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1024,9 +1036,22 @@
           <t>OFFICE_TEL</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr"/>
-      <c r="E12" s="17" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>客戶未勾選</t>
+        </is>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>不需異動</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1044,13 +1069,22 @@
           <t>(固定值 SyncSettings.DefaultPassword)</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="17" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>建議「否」— 通常不因資料同步重設既有密碼</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>客戶未勾選 — 不因資料同步重設既有密碼</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>不需異動</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="12" t="inlineStr">
@@ -1060,7 +1094,7 @@
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>employeeId = 104 EMP_NO　（現行新增時查重複用此鍵，如需異動可在此欄修改）</t>
+          <t>employeeId = 104 EMP_NO　（現行查重複/UPDATE 比對鍵，客戶未提出異動）</t>
         </is>
       </c>
     </row>
@@ -1077,13 +1111,13 @@
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>104 來源欄位 / 現行新增邏輯</t>
+          <t>104 來源欄位 / 現行邏輯</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
           <t>資料異動時
-是否需要更新 (是/否)</t>
+是否需要更新</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1093,41 +1127,48 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
+          <t>實作狀態
+(2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>organizationOID</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>nchar(32)</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>查詢 OrganizationUnit（依 DEPT1_CODE）</t>
         </is>
       </c>
-      <c r="D18" s="14" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E18" s="15" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>員工調部門(DEPT1_CODE 異動)時，覆蓋更新此欄位</t>
         </is>
       </c>
-      <c r="F18" s="15" t="inlineStr">
-        <is>
-          <t>範例列，正式填寫時請覆蓋</t>
-        </is>
-      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1145,11 +1186,24 @@
           <t>QUIT_DATE</t>
         </is>
       </c>
-      <c r="D19" s="16" t="inlineStr"/>
-      <c r="E19" s="17" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>離職日期，建議務必更新</t>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆確認需要更新</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>離職日期</t>
         </is>
       </c>
     </row>
@@ -1169,13 +1223,22 @@
           <t>查詢 Users（依 EMP_NO）</t>
         </is>
       </c>
-      <c r="D20" s="16" t="inlineStr"/>
-      <c r="E20" s="17" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>系統關聯鍵，理論上不應變動</t>
-        </is>
-      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>客戶未勾選 — 系統關聯鍵，理論上不應變動</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>不需異動</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="12" t="inlineStr">
@@ -1185,7 +1248,7 @@
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>GEN01 = 104 EMP_NO　（現行新增時查重複用此鍵，如需異動可在此欄修改）</t>
+          <t>GEN01 = 104 EMP_NO　（現行查重複/UPDATE 比對鍵，客戶未提出異動）</t>
         </is>
       </c>
     </row>
@@ -1202,13 +1265,13 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>104 來源欄位 / 現行新增邏輯</t>
+          <t>104 來源欄位 / 現行邏輯</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
           <t>資料異動時
-是否需要更新 (是/否)</t>
+是否需要更新</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1218,41 +1281,48 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
+          <t>實作狀態
+(2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>GENACTI</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>WORK_STATUS (=3→'N', 其他→'Y')</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E25" s="15" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>104 WORK_STATUS 異動為離職時，更新為 'N'</t>
         </is>
       </c>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>範例列，正式填寫時請覆蓋</t>
-        </is>
-      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -1270,11 +1340,24 @@
           <t>EMP_NAME</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>改名時是否需要更新</t>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆確認需要更新</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>改名時同步更新</t>
         </is>
       </c>
     </row>
@@ -1291,16 +1374,25 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>目前未寫入（可用 DEPT1_CODE）</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>部門代號，待確認是否納入更新</t>
-        </is>
-      </c>
+          <t>DEPT1_CODE</t>
+        </is>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆確認需要更新（部門代號，例如 A0340）</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -1315,74 +1407,220 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>目前未寫入（可用 JOB_NAME）</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr"/>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>職稱，待確認是否納入更新</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>職稱。曾評估改查 BPM Functions 取得，2026-07-18 客戶回覆暫不實作</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>暫緩（無資料來源）</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>維持 NULL，同步程式不觸碰 Functions 表</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>GEN06</t>
+          <t>GEN05</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR2(80)</t>
+          <t>VARCHAR2(5)</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>目前未寫入（可用 OFFICE_EMAIL）</t>
-        </is>
-      </c>
-      <c r="D29" s="16" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>Email，待確認是否納入更新</t>
+          <t>OFFICE_TEL_EXT</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>與 INSERT 邏輯一致，一併更新保持最新</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>客戶更新表未單獨列出，依 INSERT 邏輯延伸實作</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
+          <t>GEN06</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR2(80)</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>OFFICE_EMAIL</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆確認需要更新（客戶要求必須要有）</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
           <t>GENMODU / GENDATE</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>VARCHAR2(10) / DATE</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>(系統控制)</t>
         </is>
       </c>
-      <c r="D30" s="16" t="inlineStr"/>
-      <c r="E30" s="17" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>異動時建議固定更新為 'SYNC104' / SYSDATE，非客戶決定項目</t>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>每次 UPDATE 固定更新為 'SYNC104' / SYSDATE</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>非客戶決定項目，異動時一律更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>TA_GEN07</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR2(10)</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>BPM OrganizationUnit.managerOID → Users.id</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>客戶更新表未列入異動範圍，僅於 INSERT 時寫入直屬主管工號</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>不需異動</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>如需異動時同步更新，請告知</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>TA_GEN08</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR2(30)</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
+        <is>
+          <t>客戶要求「必須要有」(銀行帳號)，但 104 員工 API 目前無此欄位</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>暫緩（無資料來源）</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>需先確認 104 是否有對應資料來源</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C22:F22"/>
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C15:F15"/>
-    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A22:B22"/>
   </mergeCells>
@@ -2331,17 +2569,17 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(固定值)</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>未寫入 (NULL)，管理類別 (1=成本中心/2=利潤中心) 待確認</t>
-        </is>
-      </c>
-      <c r="E32" s="11" t="inlineStr">
-        <is>
-          <t>待確認</t>
+          <t>固定寫 '3'（其它）。管理類別 1=成本中心/2=利潤中心/3=其它，因無資料來源可判斷 1 或 2，2026-07-16 客戶確認一律寫 3</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>固定值</t>
         </is>
       </c>
     </row>
@@ -3042,11 +3280,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="46" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -3361,12 +3599,12 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>固定 'Employee'，對應 104 何值待確認</t>
-        </is>
-      </c>
-      <c r="E15" s="11" t="inlineStr">
-        <is>
-          <t>待確認</t>
+          <t>固定 'Employee'。2026-07-16 客戶回覆：目前欄位都是塞 DEFAULT，維持固定值不用對應 104 欄位</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>固定值</t>
         </is>
       </c>
     </row>
@@ -3427,34 +3665,34 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>performForwardType</t>
+          <t>ldapid</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>nvarchar(100) NULL</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>(固定值)</t>
+          <t>EMP_EN_NAME</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>固定 0</t>
-        </is>
-      </c>
-      <c r="E18" s="10" t="inlineStr">
-        <is>
-          <t>固定值</t>
+          <t>直接對應（英文姓名）。2026-07-16 客戶回覆新增此欄位對應</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>已確認</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>userTaskDisplay</t>
+          <t>performForwardType</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -3469,7 +3707,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>固定 1</t>
+          <t>固定 0</t>
         </is>
       </c>
       <c r="E19" s="10" t="inlineStr">
@@ -3481,110 +3719,110 @@
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
+          <t>userTaskDisplay</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>(固定值)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>固定 1</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>固定值</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
           <t>createdTime</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>datetime</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>(系統時間)</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D21" s="6" t="inlineStr">
         <is>
           <t>SYSDATETIME()</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr">
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>固定值</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>→ BPM: Employee （後寫入，需先有 Users.OID + OrganizationUnit.OID）</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24" ht="28" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>BPM 欄位</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>型態</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>104 來源欄位</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>轉換規則 / 說明</t>
         </is>
       </c>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>狀態</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>OID</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>nchar(32) PK</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>(自動產生)</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>GenerateUniqueOIDAsync()</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>已確認</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>employeeId</t>
+          <t>OID</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>nvarchar(100)</t>
+          <t>nchar(32) PK</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>EMP_NO</t>
+          <t>(自動產生)</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>員工編號，UPSERT 判斷鍵</t>
+          <t>GenerateUniqueOIDAsync()</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -3596,22 +3834,22 @@
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>organizationOID</t>
+          <t>employeeId</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>nchar(32)</t>
+          <t>nvarchar(100)</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>DEPT1_CODE</t>
+          <t>EMP_NO</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>查 BPM OrganizationUnit.id = DEPT1_CODE（104 支援 5 層部門，目前僅使用第 1 層）</t>
+          <t>員工編號，UPSERT 判斷鍵</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
@@ -3623,7 +3861,7 @@
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>userOID</t>
+          <t>organizationOID</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
@@ -3633,12 +3871,12 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>EMP_NO</t>
+          <t>DEPT1_CODE</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>查同批次剛寫入的 BPM Users.id = EMP_NO，取得 Users.OID</t>
+          <t>查 BPM OrganizationUnit.id = DEPT1_CODE（104 支援 5 層部門，目前僅使用第 1 層）</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -3650,137 +3888,137 @@
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>objectVersion</t>
+          <t>userOID</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>nchar(32)</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>(固定值)</t>
+          <t>EMP_NO</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>固定寫 1</t>
-        </is>
-      </c>
-      <c r="E28" s="10" t="inlineStr">
-        <is>
-          <t>固定值</t>
+          <t>查同批次剛寫入的 BPM Users.id = EMP_NO，取得 Users.OID</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>已確認</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
+          <t>objectVersion</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>(固定值)</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>固定寫 1</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>固定值</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
           <t>validTo</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>datetime NULL</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>QUIT_DATE</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>直接對應（容錯日期解析）</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="E30" s="8" t="inlineStr">
         <is>
           <t>已確認</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>→ ERP: YCS.GEN_FILE （2026-07-14 已用客戶真實 DDL 逐欄核對，結構完全相符）</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>→ ERP: YCS.GEN_FILE （2026-07-14 已用客戶真實 DDL 逐欄核對，結構完全相符；2026-07-16 依客戶回覆補上寫入邏輯）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>BPM 欄位</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>型態</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>104 來源欄位</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D33" s="4" t="inlineStr">
         <is>
           <t>轉換規則 / 說明</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>狀態</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="inlineStr">
-        <is>
-          <t>GEN01</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>VARCHAR2(10) PK</t>
-        </is>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>EMP_NO</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>員工編號，UPSERT 判斷鍵</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>已確認</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>GEN02</t>
+          <t>GEN01</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR2(40)</t>
+          <t>VARCHAR2(10) PK</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>EMP_NAME</t>
+          <t>EMP_NO</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>直接對應</t>
+          <t>員工編號，UPSERT 判斷鍵</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
@@ -3792,66 +4030,66 @@
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>GEN03</t>
+          <t>GEN02</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR2(10)</t>
+          <t>VARCHAR2(40)</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>EMP_NAME</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>未寫入 (NULL)，部門代號待對應（可用 DEPT1_CODE）</t>
-        </is>
-      </c>
-      <c r="E35" s="11" t="inlineStr">
-        <is>
-          <t>待確認</t>
+          <t>直接對應</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>已確認</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>GEN04</t>
+          <t>GEN03</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR2(80)</t>
+          <t>VARCHAR2(10)</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DEPT1_CODE</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>未寫入 (NULL)，職稱待對應（可用 JOB_NAME）</t>
-        </is>
-      </c>
-      <c r="E36" s="11" t="inlineStr">
-        <is>
-          <t>待確認</t>
+          <t>部門代號，客戶回覆範例「A0340」，直接對應 104 DEPT1_CODE</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>已確認</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>GEN05</t>
+          <t>GEN04</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR2(5)</t>
+          <t>VARCHAR2(80)</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -3861,7 +4099,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>未寫入 (NULL)</t>
+          <t>職稱。曾評估用 104 JOB_NAME 比對 BPM FunctionDefinition 並寫入 Functions 職務指派，2026-07-18 客戶回覆此部分暫不實作 (Functions 表先不動)，維持 NULL</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
@@ -3873,49 +4111,50 @@
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>GEN06</t>
+          <t>GEN05</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR2(80)</t>
+          <t>VARCHAR2(5)</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>OFFICE_TEL_EXT</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>未寫入 (NULL)，Email 待對應（可用 OFFICE_EMAIL）</t>
-        </is>
-      </c>
-      <c r="E38" s="11" t="inlineStr">
-        <is>
-          <t>待確認</t>
+          <t>分機，客戶回覆「有的話填入，沒有就空白」</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>已確認</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>GENACTI</t>
+          <t>GEN06</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR2(1)</t>
+          <t>VARCHAR2(80)</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>WORK_STATUS</t>
-        </is>
-      </c>
-      <c r="D39" s="6">
-        <f> 3（離職）→ 'N'；其他 → 'Y'</f>
-        <v/>
+          <t>OFFICE_EMAIL</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>Email，客戶回覆「一定要有」；若 104 未回傳則寫入空值並記錄 Warning 提醒</t>
+        </is>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
@@ -3926,34 +4165,33 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>GENUSER</t>
+          <t>GENACTI</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR2(10)</t>
+          <t>VARCHAR2(1)</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>(固定值)</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>固定 'SYNC104'</t>
-        </is>
-      </c>
-      <c r="E40" s="10" t="inlineStr">
-        <is>
-          <t>固定值</t>
+          <t>WORK_STATUS</t>
+        </is>
+      </c>
+      <c r="D40" s="6">
+        <f> 3（離職）→ 'N'；其他 → 'Y'。客戶回覆確認固定為 Y 或 N</f>
+        <v/>
+      </c>
+      <c r="E40" s="8" t="inlineStr">
+        <is>
+          <t>已確認</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>GENGRUP</t>
+          <t>GENUSER</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
@@ -3963,24 +4201,24 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(固定值)</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>未寫入 (NULL)</t>
-        </is>
-      </c>
-      <c r="E41" s="11" t="inlineStr">
-        <is>
-          <t>待確認</t>
+          <t>固定 'SYNC104'</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>固定值</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>GENMODU</t>
+          <t>GENGRUP</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
@@ -3990,39 +4228,39 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>(固定值)</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>固定 'SYNC104'</t>
-        </is>
-      </c>
-      <c r="E42" s="10" t="inlineStr">
-        <is>
-          <t>固定值</t>
+          <t>未寫入 (NULL)。2026-07-16 客戶回覆「暫時OK」，維持 NULL</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>待確認</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>GENDATE</t>
+          <t>GENMODU</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>DATE</t>
+          <t>VARCHAR2(10)</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>(系統時間)</t>
+          <t>(固定值)</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>SYSDATE</t>
+          <t>固定 'SYNC104'</t>
         </is>
       </c>
       <c r="E43" s="10" t="inlineStr">
@@ -4034,73 +4272,116 @@
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>TA_GEN07</t>
+          <t>GENDATE</t>
         </is>
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>VARCHAR2(10)</t>
+          <t>DATE</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>(系統時間)</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>未寫入 (NULL)，客製欄位待對應</t>
-        </is>
-      </c>
-      <c r="E44" s="11" t="inlineStr">
-        <is>
-          <t>待確認</t>
+          <t>SYSDATE</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
+        <is>
+          <t>固定值</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
+          <t>TA_GEN07</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>VARCHAR2(10)</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>BPM OrganizationUnit.managerOID → Users.id</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>直屬主管工號。客戶回覆「請填入直屬主管的工號」，依員工所屬部門的 managerOID 查詢對應 Users.id</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>已確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
           <t>TA_GEN08</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>VARCHAR2(30)</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>未寫入 (NULL)，客製欄位待對應</t>
-        </is>
-      </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>員工銀行帳號。客戶回覆「必須要有，不然報表會有資料錯誤」，但 104 員工 API 目前的資料模型 (Models/Employee.cs) 完全沒有銀行帳號欄位，需先請客戶/104 確認資料來源；程式已加執行期 Warning 提醒，但尚未寫入</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>待確認</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="34" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>104 員工資料實際支援 5 層部門欄位 (DEPT1_CODE ~ DEPT5_CODE)，目前程式僅使用第一層 DEPT1_CODE 作為員工所屬部門，未來若客戶需要多層部門歸屬，需額外調整 Employee.organizationOID 的對應邏輯。
-GEN03/GEN04/GEN06 目前雖標「待確認」，但依 104 資料模型可直接對應 DEPT1_CODE/JOB_NAME/OFFICE_EMAIL，待業務單位確認欄位語意後即可補上寫入邏輯，欄位本身在客戶資料庫已確認存在。</t>
+    <row r="48" ht="22" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>GEN04 職稱 — 暫緩實作紀錄 (2026-07-18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="34" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>曾評估的做法：用 104 emp.JOB_NAME 比對 BPM FunctionDefinition.functionDefinitionName (限定同一公司 organizationOID)，找到則新增一筆 Functions 職務指派 (isMain=1)，並將員工原本 isMain=1 的舊職務列改為 isMain=0 (Functions 表無失效欄位，改用 isMain 降級保留歷史)；specifiedManagerOID、approvalLevelOID 因會影響簽核路由且無法可靠推導，原規劃維持 NULL。
+2026-07-18 客戶回覆：職稱與 Functions 表這部分先不做。GEN04 暫不寫入 (維持 NULL)，同步程式完全不觸碰 BPM Functions / FunctionDefinition 資料表。上述設計先記錄於此，供日後需要時參考。</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="34" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>104 員工資料實際支援 5 層部門欄位 (DEPT1_CODE ~ DEPT5_CODE)，目前程式僅使用第一層 DEPT1_CODE 作為員工所屬部門，未來若客戶需要多層部門歸屬，需額外調整 Employee.organizationOID 的對應邏輯。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A48:E48"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A51:E51"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A31:E31"/>
-    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A32:E32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4112,7 +4393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -4246,12 +4527,12 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>僅新增、未更新</t>
+          <t>UPDATE 邏輯已依客戶回覆啟用 (2026-07-16 修正)</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>所有目標表的 UPDATE 邏輯已寫成程式碼但被註解停用，104 端資料異動目前不會回寫覆蓋既有紀錄</t>
+          <t>原本所有目標表僅 INSERT-or-SKIP，104 端資料異動不會回寫。現已依客戶回覆 DataMappingUserConfirm20260716.xlsx，針對確認需要異動的欄位啟用 UPDATE，詳見 7/8/9 更新 Mapping 分頁；description (OrganizationUnitLevel)、TA_GEN08 (銀行帳號) 因無資料來源暫緩</t>
         </is>
       </c>
     </row>
@@ -4294,34 +4575,46 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>員工僅取第一層部門</t>
+          <t>GEN_FILE 欄位已依客戶回覆補齊 (2026-07-16 修正)</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>104 員工資料含 5 層部門欄位 (DEPT1_CODE ~ DEPT5_CODE)，現行同步僅使用 DEPT1_CODE</t>
+          <t>GEN03/GEN05/GEN06/TA_GEN07 已補上寫入邏輯；GEN04 (職稱) 曾評估改查 BPM Functions 取得，2026-07-18 客戶回覆暫不實作，維持 NULL；TA_GEN08 (銀行帳號) 因 104 員工 API 無對應欄位，暫緩並於執行期記錄 Warning</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>BatchSize 未實際分批</t>
+          <t>員工僅取第一層部門</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>appsettings.json 的 SyncSettings.BatchSize 僅用於進度 Log 顯示頻率，資料庫寫入仍是單一大交易逐筆執行</t>
+          <t>104 員工資料含 5 層部門欄位 (DEPT1_CODE ~ DEPT5_CODE)，現行同步僅使用 DEPT1_CODE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
+          <t>BatchSize 未實際分批</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>appsettings.json 的 SyncSettings.BatchSize 僅用於進度 Log 顯示頻率，資料庫寫入仍是單一大交易逐筆執行</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
           <t>多筆欄位待確認</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>詳見各分頁「狀態」欄標示「待確認」的欄位，需與客戶 ERP/BPM 管理端進一步確認正式對應規則</t>
         </is>
@@ -4344,15 +4637,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4365,14 +4659,14 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>現行程式僅在部門已存在時「跳過(SKIP)」，並不會更新既有資料。以下請客戶確認：資料異動時應以哪個欄位判斷唯一值、需要更新哪些欄位。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
+          <t>2026-07-16 依客戶回覆 DataMappingUserConfirm20260716.xlsx 定案，程式已同步更新 UPDATE 邏輯 (BpmDatabaseService.cs / ErpDatabaseService.cs)。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>填寫說明：黃色儲存格為需要客戶確認/填寫的欄位。第一列(綠色斜體)為範例，僅供參考格式，非實際資料，正式填寫時請覆蓋或刪除。「是否需要更新」請填「是」或「否」；填「是」的欄位請在「更新規則/資料來源說明」註明依 104 哪個欄位、什麼條件更新。</t>
+          <t>2026-07-16 更新：客戶已於 DataMappingUserConfirm20260716.xlsx 回覆各欄位是否需要更新，本頁已依回覆內容定案。「實作狀態」欄位說明：綠色「已實作」代表程式已於 2026-07-16 加入對應 UPDATE 邏輯；橘色「暫緩」代表客戶雖回覆需要更新，但目前完全沒有資料來源可供寫入，貿然實作可能誤蓋既有資料，故暫緩，待補充資料來源後再開發；灰色「不需異動」代表客戶回覆或既有邏輯判斷不需要更新此欄位。</t>
         </is>
       </c>
     </row>
@@ -4384,7 +4678,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>id = 104 DEPT_CODE　（現行新增時查重複用此鍵，如需異動可在此欄修改）</t>
+          <t>id = 104 DEPT_CODE　（現行查重複/UPDATE 比對鍵，客戶未提出異動）</t>
         </is>
       </c>
     </row>
@@ -4401,13 +4695,13 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>104 來源欄位 / 現行新增邏輯</t>
+          <t>104 來源欄位 / 現行邏輯</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
           <t>資料異動時
-是否需要更新 (是/否)</t>
+是否需要更新</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -4417,41 +4711,48 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
+          <t>實作狀態
+(2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>organizationUnitName</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>nvarchar(100)</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>DEPT_NAME</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>104 DEPT_NAME 異動時，覆蓋更新此欄位</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>範例列，正式填寫時請覆蓋</t>
-        </is>
-      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -4469,9 +4770,22 @@
           <t>查詢 Users（依 LEADER_EMP_NO）</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="17" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆確認需要更新</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -4489,9 +4803,22 @@
           <t>查詢 OrganizationUnit（依 PARENT_DEPT_CODE）</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr"/>
-      <c r="E11" s="17" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆確認需要更新</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>若父部門異動，可能需連動調整組織樹</t>
         </is>
@@ -4513,9 +4840,22 @@
           <t>查詢 OrganizationUnitLevel（依 DEPT_LEVEL_ID）</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr"/>
-      <c r="E12" s="17" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆確認需要更新</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -4533,13 +4873,22 @@
           <t>查詢 Organization（依 CO_CODE）</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr"/>
-      <c r="E13" s="17" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>理論上不會變動</t>
-        </is>
-      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>客戶未勾選，理論上部門不會換公司</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>不需異動</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -4557,11 +4906,24 @@
           <t>IS_ACT (1→1, 其他→0)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr"/>
-      <c r="E14" s="17" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>部門停用/啟用狀態，建議務必更新</t>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆確認需要更新</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>部門停用/啟用狀態</t>
         </is>
       </c>
     </row>
@@ -4581,11 +4943,24 @@
           <t>(系統控制，異動慣例為 +1)</t>
         </is>
       </c>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="17" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>非資料欄位，通常不需客戶決定</t>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>－</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>每次 UPDATE 自動 +1</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>非資料欄位，不需客戶決定</t>
         </is>
       </c>
     </row>
@@ -4597,7 +4972,7 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>GEM01 = 104 DEPT_CODE　（現行新增時查重複用此鍵，如需異動可在此欄修改）</t>
+          <t>GEM01 = 104 DEPT_CODE　（現行查重複/UPDATE 比對鍵，客戶未提出異動）</t>
         </is>
       </c>
     </row>
@@ -4614,13 +4989,13 @@
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>104 來源欄位 / 現行新增邏輯</t>
+          <t>104 來源欄位 / 現行邏輯</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
           <t>資料異動時
-是否需要更新 (是/否)</t>
+是否需要更新</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -4630,41 +5005,48 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
+          <t>實作狀態
+(2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>GEM02</t>
         </is>
       </c>
-      <c r="B20" s="14" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>VARCHAR2(80)</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>DEPT_NAME</t>
         </is>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E20" s="15" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>104 DEPT_NAME 異動時，覆蓋更新此欄位</t>
         </is>
       </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>範例列，正式填寫時請覆蓋</t>
-        </is>
-      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -4682,9 +5064,22 @@
           <t>DEPT_ABBR（無則用 DEPT_NAME）</t>
         </is>
       </c>
-      <c r="D21" s="16" t="inlineStr"/>
-      <c r="E21" s="17" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆確認需要更新</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -4702,11 +5097,24 @@
           <t>目前未寫入</t>
         </is>
       </c>
-      <c r="D22" s="16" t="inlineStr"/>
-      <c r="E22" s="17" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>欄位用途待確認</t>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>客戶未勾選</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>不需異動</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>欄位用途仍待確認</t>
         </is>
       </c>
     </row>
@@ -4726,11 +5134,24 @@
           <t>目前未寫入</t>
         </is>
       </c>
-      <c r="D23" s="16" t="inlineStr"/>
-      <c r="E23" s="17" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>是否為會計部門，待確認</t>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>客戶未勾選</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>不需異動</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>是否為會計部門，仍待確認</t>
         </is>
       </c>
     </row>
@@ -4750,11 +5171,24 @@
           <t>目前未寫入</t>
         </is>
       </c>
-      <c r="D24" s="16" t="inlineStr"/>
-      <c r="E24" s="17" t="inlineStr"/>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>費用類別，待確認</t>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>客戶未勾選</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>不需異動</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>費用類別，仍待確認</t>
         </is>
       </c>
     </row>
@@ -4774,11 +5208,24 @@
           <t>IS_ACT (1→'Y', 其他→'N')</t>
         </is>
       </c>
-      <c r="D25" s="16" t="inlineStr"/>
-      <c r="E25" s="17" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>部門停用/啟用狀態，建議務必更新</t>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆確認需要更新</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>部門停用/啟用狀態</t>
         </is>
       </c>
     </row>
@@ -4798,9 +5245,22 @@
           <t>目前未寫入</t>
         </is>
       </c>
-      <c r="D26" s="16" t="inlineStr"/>
-      <c r="E26" s="17" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>客戶未勾選</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>不需異動</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -4815,14 +5275,27 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>目前未寫入</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr"/>
-      <c r="E27" s="17" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>管理類別，待確認</t>
+          <t>(固定值 '3')</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>是，預設3</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆：管理類別 1.成本中心 2.利潤中心 3.其它，無法判斷時固定寫 3</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>INSERT 也已同步改為固定寫 '3'，見 2_部門Department 分頁</t>
         </is>
       </c>
     </row>
@@ -4842,11 +5315,24 @@
           <t>目前未寫入</t>
         </is>
       </c>
-      <c r="D28" s="16" t="inlineStr"/>
-      <c r="E28" s="17" t="inlineStr"/>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>對應成本中心，待確認</t>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>客戶未勾選</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>不需異動</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>對應成本中心，仍待確認</t>
         </is>
       </c>
     </row>
@@ -4866,23 +5352,36 @@
           <t>(系統控制)</t>
         </is>
       </c>
-      <c r="D29" s="16" t="inlineStr"/>
-      <c r="E29" s="17" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>異動時建議固定更新為 'SYNC104' / SYSDATE，非客戶決定項目</t>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>每次 UPDATE 固定更新為 'SYNC104' / SYSDATE</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>非客戶決定項目，異動時一律更新</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="C17:F17"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C17:G17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4894,15 +5393,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4915,14 +5415,14 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>現行程式僅在資料已存在時「跳過(SKIP)」，並不會更新既有資料。以下請客戶確認：資料異動時應以哪個欄位判斷唯一值、需要更新哪些欄位。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="34" customHeight="1">
+          <t>2026-07-16 依客戶回覆 DataMappingUserConfirm20260716.xlsx 定案，程式已同步更新 UPDATE 邏輯。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>填寫說明：黃色儲存格為需要客戶確認/填寫的欄位。第一列(綠色斜體)為範例，僅供參考格式，非實際資料，正式填寫時請覆蓋或刪除。「是否需要更新」請填「是」或「否」；填「是」的欄位請在「更新規則/資料來源說明」註明依 104 哪個欄位、什麼條件更新。</t>
+          <t>2026-07-16 更新：客戶已於 DataMappingUserConfirm20260716.xlsx 回覆各欄位是否需要更新，本頁已依回覆內容定案。「實作狀態」欄位說明：綠色「已實作」代表程式已於 2026-07-16 加入對應 UPDATE 邏輯；橘色「暫緩」代表客戶雖回覆需要更新，但目前完全沒有資料來源可供寫入，貿然實作可能誤蓋既有資料，故暫緩，待補充資料來源後再開發；灰色「不需異動」代表客戶回覆或既有邏輯判斷不需要更新此欄位。</t>
         </is>
       </c>
     </row>
@@ -4934,7 +5434,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>levelValue + organizationOID　（現行新增時查重複用此複合鍵，如需異動可在此欄修改）</t>
+          <t>levelValue + organizationOID　（現行查重複/UPDATE 比對鍵，客戶未提出異動）</t>
         </is>
       </c>
     </row>
@@ -4951,13 +5451,13 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>104 來源欄位 / 現行新增邏輯</t>
+          <t>104 來源欄位 / 現行邏輯</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
           <t>資料異動時
-是否需要更新 (是/否)</t>
+是否需要更新</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -4967,41 +5467,48 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
+          <t>實作狀態
+(2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>organizationUnitLevelName</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>nvarchar(100)</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>LEVEL_NAME</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>104 LEVEL_NAME 異動時，覆蓋更新此欄位</t>
         </is>
       </c>
-      <c r="F9" s="15" t="inlineStr">
-        <is>
-          <t>範例列，正式填寫時請覆蓋</t>
-        </is>
-      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -5019,9 +5526,26 @@
           <t>目前未寫入</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr"/>
-      <c r="E10" s="17" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr"/>
+      <c r="D10" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>客戶回覆確認需要更新，但目前完全沒有 104 資料來源可供寫入 (現行仍是 NULL)，貿然 UPDATE 只會覆蓋成 NULL、可能誤刪既有人工填寫內容，故暫緩實作</t>
+        </is>
+      </c>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>暫緩（無資料來源）</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>待客戶提供 description 的資料來源後再開發</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -5031,7 +5555,7 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>ABD01 + ABD02 (複合鍵)　（現行新增時查重複用此複合鍵，如需異動可在此欄修改）</t>
+          <t>ABD01 + ABD02 (複合鍵)　（現行查重複/UPDATE 比對鍵，客戶未提出異動）</t>
         </is>
       </c>
     </row>
@@ -5048,13 +5572,13 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>104 來源欄位 / 現行新增邏輯</t>
+          <t>104 來源欄位 / 現行邏輯</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
           <t>資料異動時
-是否需要更新 (是/否)</t>
+是否需要更新</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -5064,39 +5588,50 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
+          <t>實作狀態
+(2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
           <t>備註</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>ABDACTI</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>VARCHAR2(1)</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>(固定值 'Y')</t>
         </is>
       </c>
-      <c r="D15" s="14" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>部門停用或父子關係失效時，更新為 'N'</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
-        <is>
-          <t>範例列，正式填寫時請覆蓋</t>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>目前程式固定寫 'Y'，尚未實作停用時改 'N' 的判斷條件</t>
         </is>
       </c>
     </row>
@@ -5116,9 +5651,22 @@
           <t>目前未寫入</t>
         </is>
       </c>
-      <c r="D16" s="16" t="inlineStr"/>
-      <c r="E16" s="17" t="inlineStr"/>
-      <c r="F16" s="6" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>客戶未勾選</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>不需異動</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -5136,38 +5684,51 @@
           <t>(系統控制)</t>
         </is>
       </c>
-      <c r="D17" s="16" t="inlineStr"/>
-      <c r="E17" s="17" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>異動時建議固定更新為 'SYNC104' / SYSDATE，非客戶決定項目</t>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>每次 UPDATE 固定更新為 'SYNC104' / SYSDATE</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>已實作 (2026-07-16)</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>非客戶決定項目，異動時一律更新</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>⚠ 需要客戶特別確認的業務邏輯問題</t>
+          <t>⚠ 仍需要客戶特別確認的業務邏輯問題</t>
         </is>
       </c>
     </row>
     <row r="20" ht="34" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>若部門的「父部門」異動（例如整個部門被移到別的上層部門），ABD01（父層代碼）會跟著改變，等於變成一組新的複合鍵 (ABD01+ABD02)，而不是單純 UPDATE 既有那一列。
-請客戶確認：這種情況要「新增一筆新關係 + 把舊關係標記失效 (ABDACTI='N')」，還是有其他處理方式？此欄位由客戶填寫：＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿＿</t>
+          <t>1) 若部門的「父部門」異動（例如整個部門被移到別的上層部門），ABD01（父層代碼）會跟著改變，等於變成一組新的複合鍵 (ABD01+ABD02)，而不是單純 UPDATE 既有那一列。目前程式尚未處理這種情況，請客戶確認：要「新增一筆新關係 + 把舊關係標記失效 (ABDACTI='N')」，還是有其他處理方式？
+2) ABDACTI 目前 INSERT/UPDATE 都固定寫 'Y'，尚未實作「部門停用時自動改寫 'N'」的判斷條件，若需要這項邏輯，麻煩確認判斷依據 (例如依 Department.IsAct)。</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="C12:F12"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A19:G19"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A12:B12"/>
   </mergeCells>
